--- a/Daily_Report/Top 7 broker List with its Turnover 2023-01-18.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2023-01-18.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="271">
   <si>
     <t>Date: 2023-01-18</t>
   </si>
@@ -581,16 +581,22 @@
     <t>163,673,289.8</t>
   </si>
   <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>69,118,364.2</t>
+  </si>
+  <si>
     <t>Promoter Shares/debenture</t>
   </si>
   <si>
-    <t>114,245,226.5</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>69,118,364.2</t>
+    <t>61,445,928.8</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>52,799,297.7</t>
   </si>
   <si>
     <t>Mutual Fund</t>
@@ -785,13 +791,13 @@
     <t>14,795,231.0</t>
   </si>
   <si>
-    <t>11,407,760.5</t>
-  </si>
-  <si>
     <t>10,505,615.3</t>
   </si>
   <si>
     <t>10,124,288.8</t>
+  </si>
+  <si>
+    <t>10,123,379.6</t>
   </si>
   <si>
     <t>72,617,502.4</t>
@@ -1320,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V45"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2546,7 +2552,7 @@
         <v>189</v>
       </c>
       <c r="D41" s="22">
-        <v>0.02317951752340748</v>
+        <v>0.01402360854143136</v>
       </c>
     </row>
     <row r="42" spans="2:4">
@@ -2557,7 +2563,7 @@
         <v>191</v>
       </c>
       <c r="D42" s="22">
-        <v>0.01402360854143136</v>
+        <v>0.01246692773952922</v>
       </c>
     </row>
     <row r="43" spans="2:4">
@@ -2568,7 +2574,7 @@
         <v>193</v>
       </c>
       <c r="D43" s="22">
-        <v>0.00230772713921892</v>
+        <v>0.01071258978387826</v>
       </c>
     </row>
     <row r="44" spans="2:4">
@@ -2579,18 +2585,29 @@
         <v>195</v>
       </c>
       <c r="D44" s="22">
-        <v>0.0003611537984047489</v>
+        <v>0.00230772713921892</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="22">
+        <v>0.0003611537984047489</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" s="20" t="s">
         <v>198</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2972,7 +2989,7 @@
         <v>168</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D9" s="10">
         <v>0.2344928873524849</v>
@@ -2981,7 +2998,7 @@
         <v>168</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G9" s="12">
         <v>0.1691595283153622</v>
@@ -2990,7 +3007,7 @@
         <v>168</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J9" s="14">
         <v>0.2293448822411044</v>
@@ -2999,7 +3016,7 @@
         <v>168</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="M9" s="16">
         <v>0.1987478979598465</v>
@@ -3008,7 +3025,7 @@
         <v>168</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P9" s="18">
         <v>0.2318518444505923</v>
@@ -3017,7 +3034,7 @@
         <v>168</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="S9" s="16">
         <v>0.1617400084257393</v>
@@ -3026,7 +3043,7 @@
         <v>168</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="V9" s="18">
         <v>0.3180524209456988</v>
@@ -3038,7 +3055,7 @@
         <v>178</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D10" s="10">
         <v>0.05354952348582318</v>
@@ -3047,7 +3064,7 @@
         <v>172</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G10" s="12">
         <v>0.02920365786159057</v>
@@ -3056,7 +3073,7 @@
         <v>170</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J10" s="14">
         <v>0.04811802999400269</v>
@@ -3065,7 +3082,7 @@
         <v>170</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M10" s="16">
         <v>0.03842628692888984</v>
@@ -3074,7 +3091,7 @@
         <v>170</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P10" s="18">
         <v>0.1020713883553308</v>
@@ -3083,7 +3100,7 @@
         <v>174</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="S10" s="16">
         <v>0.1070655374488539</v>
@@ -3092,7 +3109,7 @@
         <v>172</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="V10" s="18">
         <v>0.04791983548110829</v>
@@ -3104,7 +3121,7 @@
         <v>170</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D11" s="10">
         <v>0.0527880998193309</v>
@@ -3113,7 +3130,7 @@
         <v>170</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G11" s="12">
         <v>0.02608898441690451</v>
@@ -3122,7 +3139,7 @@
         <v>172</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J11" s="14">
         <v>0.03010269286105165</v>
@@ -3131,7 +3148,7 @@
         <v>174</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M11" s="16">
         <v>0.02992832132274532</v>
@@ -3140,7 +3157,7 @@
         <v>180</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P11" s="18">
         <v>0.04620523825807386</v>
@@ -3149,7 +3166,7 @@
         <v>172</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="S11" s="16">
         <v>0.1018309269725642</v>
@@ -3158,7 +3175,7 @@
         <v>174</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="V11" s="18">
         <v>0.04641372410991509</v>
@@ -3170,7 +3187,7 @@
         <v>174</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D12" s="10">
         <v>0.02548081737584901</v>
@@ -3179,7 +3196,7 @@
         <v>180</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G12" s="12">
         <v>0.02299251447151865</v>
@@ -3188,7 +3205,7 @@
         <v>174</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J12" s="14">
         <v>0.02934313918325604</v>
@@ -3197,7 +3214,7 @@
         <v>172</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M12" s="16">
         <v>0.02758177942105461</v>
@@ -3206,7 +3223,7 @@
         <v>172</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P12" s="18">
         <v>0.02652604987370841</v>
@@ -3215,7 +3232,7 @@
         <v>170</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="S12" s="16">
         <v>0.02811148061420803</v>
@@ -3224,7 +3241,7 @@
         <v>176</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="V12" s="18">
         <v>0.03927150761687653</v>
@@ -3236,7 +3253,7 @@
         <v>172</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D13" s="10">
         <v>0.02189343530268901</v>
@@ -3245,7 +3262,7 @@
         <v>176</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G13" s="12">
         <v>0.02184876748474861</v>
@@ -3254,7 +3271,7 @@
         <v>182</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J13" s="14">
         <v>0.02427758223689919</v>
@@ -3263,7 +3280,7 @@
         <v>182</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M13" s="16">
         <v>0.02666577475478219</v>
@@ -3272,7 +3289,7 @@
         <v>182</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P13" s="18">
         <v>0.02398128964133277</v>
@@ -3281,7 +3298,7 @@
         <v>182</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="S13" s="16">
         <v>0.01542326414438575</v>
@@ -3290,7 +3307,7 @@
         <v>186</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="V13" s="18">
         <v>0.0339247134644667</v>
@@ -3370,7 +3387,7 @@
         <v>168</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D16" s="10">
         <v>0.2948348751820162</v>
@@ -3379,7 +3396,7 @@
         <v>168</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G16" s="12">
         <v>0.1963795740003537</v>
@@ -3388,7 +3405,7 @@
         <v>168</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J16" s="14">
         <v>0.2515696454717546</v>
@@ -3397,7 +3414,7 @@
         <v>168</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M16" s="16">
         <v>0.2759286012699002</v>
@@ -3406,7 +3423,7 @@
         <v>168</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P16" s="18">
         <v>0.2239215661427141</v>
@@ -3415,7 +3432,7 @@
         <v>168</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="S16" s="16">
         <v>0.2235999874266345</v>
@@ -3424,7 +3441,7 @@
         <v>168</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="V16" s="18">
         <v>0.2106894546594955</v>
@@ -3436,7 +3453,7 @@
         <v>178</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D17" s="10">
         <v>0.05903180060553508</v>
@@ -3445,7 +3462,7 @@
         <v>174</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G17" s="12">
         <v>0.1110252166103692</v>
@@ -3454,7 +3471,7 @@
         <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J17" s="14">
         <v>0.07095871534989324</v>
@@ -3463,7 +3480,7 @@
         <v>174</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M17" s="16">
         <v>0.06113811146558264</v>
@@ -3472,7 +3489,7 @@
         <v>176</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="P17" s="18">
         <v>0.04300507521611586</v>
@@ -3481,7 +3498,7 @@
         <v>172</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="S17" s="16">
         <v>0.06930378406852894</v>
@@ -3490,7 +3507,7 @@
         <v>172</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="V17" s="18">
         <v>0.03513336637281355</v>
@@ -3502,7 +3519,7 @@
         <v>170</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D18" s="10">
         <v>0.03930354658652405</v>
@@ -3511,7 +3528,7 @@
         <v>180</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G18" s="12">
         <v>0.07726704334019761</v>
@@ -3520,7 +3537,7 @@
         <v>184</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J18" s="14">
         <v>0.05322798084764343</v>
@@ -3529,25 +3546,25 @@
         <v>170</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M18" s="16">
         <v>0.04961475890138673</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P18" s="18">
-        <v>0.03315876570970305</v>
+        <v>0.03053651383801156</v>
       </c>
       <c r="Q18" s="15" t="s">
         <v>180</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="S18" s="16">
         <v>0.05174342202757065</v>
@@ -3556,7 +3573,7 @@
         <v>174</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="V18" s="18">
         <v>0.03238996767066543</v>
@@ -3568,7 +3585,7 @@
         <v>182</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D19" s="10">
         <v>0.03802324953715826</v>
@@ -3577,7 +3594,7 @@
         <v>172</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G19" s="12">
         <v>0.06262297825045701</v>
@@ -3586,7 +3603,7 @@
         <v>170</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J19" s="14">
         <v>0.03117630623086899</v>
@@ -3595,25 +3612,25 @@
         <v>172</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M19" s="16">
         <v>0.04643152783996525</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03053651383801156</v>
+        <v>0.02942811784105834</v>
       </c>
       <c r="Q19" s="15" t="s">
         <v>174</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="S19" s="16">
         <v>0.0438564645390071</v>
@@ -3622,7 +3639,7 @@
         <v>182</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="V19" s="18">
         <v>0.02532635033740556</v>
@@ -3634,7 +3651,7 @@
         <v>176</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D20" s="10">
         <v>0.02640049865348758</v>
@@ -3643,7 +3660,7 @@
         <v>178</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G20" s="12">
         <v>0.04250634232072827</v>
@@ -3652,7 +3669,7 @@
         <v>182</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J20" s="14">
         <v>0.0300483150590676</v>
@@ -3661,25 +3678,25 @@
         <v>176</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M20" s="16">
         <v>0.03307771806605934</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02942811784105834</v>
+        <v>0.02942547508310569</v>
       </c>
       <c r="Q20" s="15" t="s">
         <v>170</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S20" s="16">
         <v>0.03916645083937819</v>
@@ -3688,7 +3705,7 @@
         <v>170</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="V20" s="18">
         <v>0.02274785669689157</v>
